--- a/manufacturing_forms/002_manufacturing_long_term_sick_leave_request--manufacturing_forms.xlsx
+++ b/manufacturing_forms/002_manufacturing_long_term_sick_leave_request--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1118,8 +1118,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'plant_manager'}</t>
+          <t>plant_manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Plant Manager'}</t>
+          <t>Plant Manager</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'hr_manager'}</t>
+          <t>hr_manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'HR Manager'}</t>
+          <t>HR Manager</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Declined'}</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'reopened'}</t>
+          <t>reopened</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Reopened'}</t>
+          <t>Reopened</t>
         </is>
       </c>
     </row>
